--- a/events/Duisburg_2012_WC/Duisburg_2012_WC_Results.xlsx
+++ b/events/Duisburg_2012_WC/Duisburg_2012_WC_Results.xlsx
@@ -2513,6 +2513,11 @@
           <t>00:02:04.102</t>
         </is>
       </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8692,6 +8697,11 @@
           <t>00:04:13.008</t>
         </is>
       </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -14267,6 +14277,11 @@
           <t>00:02:01.631</t>
         </is>
       </c>
+      <c r="R217" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -24393,6 +24408,11 @@
           <t>00:01:58.177</t>
         </is>
       </c>
+      <c r="R376" t="inlineStr">
+        <is>
+          <t>84718</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -31785,6 +31805,11 @@
           <t>00:02:22.039</t>
         </is>
       </c>
+      <c r="R490" t="inlineStr">
+        <is>
+          <t>84718</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -34686,6 +34711,11 @@
           <t>00:01:56.916</t>
         </is>
       </c>
+      <c r="R535" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -38775,6 +38805,11 @@
           <t>00:04:06.162</t>
         </is>
       </c>
+      <c r="R597" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -57034,6 +57069,11 @@
           <t>00:00:37.287</t>
         </is>
       </c>
+      <c r="R878" t="inlineStr">
+        <is>
+          <t>84718</t>
+        </is>
+      </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
@@ -77956,6 +77996,11 @@
           <t>00:00:37.596</t>
         </is>
       </c>
+      <c r="R1201" t="inlineStr">
+        <is>
+          <t>84718</t>
+        </is>
+      </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
@@ -82232,6 +82277,11 @@
           <t>00:01:57.736</t>
         </is>
       </c>
+      <c r="R1265" t="inlineStr">
+        <is>
+          <t>84718</t>
+        </is>
+      </c>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
@@ -87259,6 +87309,11 @@
       <c r="P1338" t="inlineStr">
         <is>
           <t>00:02:51.568</t>
+        </is>
+      </c>
+      <c r="S1338" t="inlineStr">
+        <is>
+          <t>84718</t>
         </is>
       </c>
     </row>
@@ -89136,7 +89191,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D260"/>
+  <dimension ref="A1:D262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94859,6 +94914,50 @@
         </is>
       </c>
     </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>47779</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Krisztina</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>BEDOCS</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>84718</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Nikolay</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>LIPKIN</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Duisburg_2012_WC/Duisburg_2012_WC_Results.xlsx
+++ b/events/Duisburg_2012_WC/Duisburg_2012_WC_Results.xlsx
@@ -3278,6 +3278,11 @@
           <t>00:03:38.090</t>
         </is>
       </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3658,6 +3663,11 @@
           <t>00:04:11.705</t>
         </is>
       </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>68923</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4798,6 +4808,11 @@
           <t>00:03:57.045</t>
         </is>
       </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5987,6 +6002,11 @@
           <t>00:03:34.918</t>
         </is>
       </c>
+      <c r="R89" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -7127,6 +7147,11 @@
           <t>00:04:03.712</t>
         </is>
       </c>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -10007,6 +10032,11 @@
           <t>00:03:23.540</t>
         </is>
       </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
       <c r="S152" t="inlineStr">
         <is>
           <t>42452</t>
@@ -11532,6 +11562,11 @@
           <t>46808</t>
         </is>
       </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -12192,6 +12227,11 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="T185" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -12757,6 +12797,11 @@
           <t>36600</t>
         </is>
       </c>
+      <c r="T193" t="inlineStr">
+        <is>
+          <t>36598</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -15277,6 +15322,11 @@
           <t>00:03:37.160</t>
         </is>
       </c>
+      <c r="R233" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -16872,6 +16922,11 @@
           <t>00:03:36.016</t>
         </is>
       </c>
+      <c r="R258" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -17697,6 +17752,11 @@
           <t>00:04:40.270</t>
         </is>
       </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -19519,6 +19579,11 @@
           <t>00:03:25.027</t>
         </is>
       </c>
+      <c r="R300" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
       <c r="S300" t="inlineStr">
         <is>
           <t>42452</t>
@@ -21158,6 +21223,11 @@
           <t>46808</t>
         </is>
       </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -21643,6 +21713,11 @@
           <t>36600</t>
         </is>
       </c>
+      <c r="T332" t="inlineStr">
+        <is>
+          <t>36598</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -21768,6 +21843,11 @@
           <t>00:01:45.516</t>
         </is>
       </c>
+      <c r="R334" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -23793,6 +23873,11 @@
           <t>00:01:58.080</t>
         </is>
       </c>
+      <c r="R366" t="inlineStr">
+        <is>
+          <t>68923</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -24158,6 +24243,11 @@
           <t>00:01:50.611</t>
         </is>
       </c>
+      <c r="R372" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -25098,6 +25188,11 @@
           <t>00:01:51.013</t>
         </is>
       </c>
+      <c r="R387" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -25533,6 +25628,11 @@
           <t>00:01:32.473</t>
         </is>
       </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
       <c r="S394" t="inlineStr">
         <is>
           <t>52286</t>
@@ -25858,6 +25958,11 @@
           <t>00:01:37.382</t>
         </is>
       </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -27551,6 +27656,11 @@
           <t>46808</t>
         </is>
       </c>
+      <c r="S425" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -28661,6 +28771,11 @@
           <t>42727</t>
         </is>
       </c>
+      <c r="S441" t="inlineStr">
+        <is>
+          <t>42735</t>
+        </is>
+      </c>
       <c r="T441" t="inlineStr">
         <is>
           <t>42731</t>
@@ -28736,6 +28851,11 @@
           <t>41991</t>
         </is>
       </c>
+      <c r="S442" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
       <c r="U442" t="inlineStr">
         <is>
           <t>42049</t>
@@ -29601,6 +29721,11 @@
           <t>00:01:53.720</t>
         </is>
       </c>
+      <c r="R455" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
@@ -30171,6 +30296,11 @@
           <t>00:01:56.933</t>
         </is>
       </c>
+      <c r="R464" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
@@ -30225,6 +30355,11 @@
           <t>00:02:47.672</t>
         </is>
       </c>
+      <c r="R465" t="inlineStr">
+        <is>
+          <t>68923</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
@@ -32690,6 +32825,11 @@
           <t>00:01:38.193</t>
         </is>
       </c>
+      <c r="R504" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -34093,6 +34233,11 @@
           <t>46808</t>
         </is>
       </c>
+      <c r="S526" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
@@ -34233,6 +34378,11 @@
           <t>41991</t>
         </is>
       </c>
+      <c r="S528" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
       <c r="U528" t="inlineStr">
         <is>
           <t>42049</t>
@@ -34303,6 +34453,11 @@
           <t>42727</t>
         </is>
       </c>
+      <c r="S529" t="inlineStr">
+        <is>
+          <t>42735</t>
+        </is>
+      </c>
       <c r="T529" t="inlineStr">
         <is>
           <t>42731</t>
@@ -36547,6 +36702,11 @@
           <t>00:03:37.963</t>
         </is>
       </c>
+      <c r="R563" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" t="inlineStr">
@@ -37872,6 +38032,11 @@
           <t>42452</t>
         </is>
       </c>
+      <c r="S583" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" t="inlineStr">
@@ -38542,6 +38707,11 @@
           <t>00:04:01.413</t>
         </is>
       </c>
+      <c r="R593" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
       <c r="S593" t="inlineStr">
         <is>
           <t>46808</t>
@@ -40251,6 +40421,11 @@
           <t>00:03:26.286</t>
         </is>
       </c>
+      <c r="R619" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
     </row>
     <row r="620">
       <c r="A620" t="inlineStr">
@@ -42745,6 +42920,11 @@
           <t>00:01:32.806</t>
         </is>
       </c>
+      <c r="S656" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
       <c r="T656" t="inlineStr">
         <is>
           <t>42059</t>
@@ -43644,6 +43824,11 @@
           <t>42049</t>
         </is>
       </c>
+      <c r="T668" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
       <c r="U668" t="inlineStr">
         <is>
           <t>41991</t>
@@ -43957,6 +44142,11 @@
           <t>42731</t>
         </is>
       </c>
+      <c r="T672" t="inlineStr">
+        <is>
+          <t>42735</t>
+        </is>
+      </c>
       <c r="U672" t="inlineStr">
         <is>
           <t>42727</t>
@@ -44482,6 +44672,11 @@
           <t>00:01:51.572</t>
         </is>
       </c>
+      <c r="S680" t="inlineStr">
+        <is>
+          <t>36598</t>
+        </is>
+      </c>
     </row>
     <row r="681">
       <c r="A681" t="inlineStr">
@@ -45066,6 +45261,11 @@
           <t>00:01:45.302</t>
         </is>
       </c>
+      <c r="S689" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="690">
       <c r="A690" t="inlineStr">
@@ -48106,6 +48306,11 @@
           <t>00:00:41.781</t>
         </is>
       </c>
+      <c r="R737" t="inlineStr">
+        <is>
+          <t>68923</t>
+        </is>
+      </c>
     </row>
     <row r="738">
       <c r="A738" t="inlineStr">
@@ -48486,6 +48691,11 @@
           <t>00:00:35.703</t>
         </is>
       </c>
+      <c r="R743" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="744">
       <c r="A744" t="inlineStr">
@@ -54701,6 +54911,11 @@
           <t>00:00:33.919</t>
         </is>
       </c>
+      <c r="R842" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
       <c r="S842" t="inlineStr">
         <is>
           <t>45844</t>
@@ -56934,6 +57149,11 @@
           <t>52286</t>
         </is>
       </c>
+      <c r="S876" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
       <c r="X876" t="inlineStr">
         <is>
           <t>DSQ</t>
@@ -57074,6 +57294,11 @@
           <t>84718</t>
         </is>
       </c>
+      <c r="S878" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="879">
       <c r="A879" t="inlineStr">
@@ -58069,6 +58294,11 @@
           <t>00:00:40.832</t>
         </is>
       </c>
+      <c r="R893" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
       <c r="S893" t="inlineStr">
         <is>
           <t>46808</t>
@@ -59119,6 +59349,11 @@
           <t>00:00:44.266</t>
         </is>
       </c>
+      <c r="S909" t="inlineStr">
+        <is>
+          <t>36598</t>
+        </is>
+      </c>
     </row>
     <row r="910">
       <c r="A910" t="inlineStr">
@@ -59764,6 +59999,11 @@
           <t>00:01:47.090</t>
         </is>
       </c>
+      <c r="S919" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="920">
       <c r="A920" t="inlineStr">
@@ -60284,6 +60524,11 @@
           <t>00:01:54.292</t>
         </is>
       </c>
+      <c r="S927" t="inlineStr">
+        <is>
+          <t>36598</t>
+        </is>
+      </c>
     </row>
     <row r="928">
       <c r="A928" t="inlineStr">
@@ -61134,6 +61379,11 @@
           <t>00:00:36.327</t>
         </is>
       </c>
+      <c r="R940" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="941">
       <c r="A941" t="inlineStr">
@@ -69459,6 +69709,11 @@
           <t>00:00:32.690</t>
         </is>
       </c>
+      <c r="R1071" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
       <c r="S1071" t="inlineStr">
         <is>
           <t>45844</t>
@@ -70194,6 +70449,11 @@
           <t>00:00:41.562</t>
         </is>
       </c>
+      <c r="R1082" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
       <c r="S1082" t="inlineStr">
         <is>
           <t>46808</t>
@@ -70724,6 +70984,11 @@
           <t>00:00:41.701</t>
         </is>
       </c>
+      <c r="S1090" t="inlineStr">
+        <is>
+          <t>36598</t>
+        </is>
+      </c>
     </row>
     <row r="1091">
       <c r="A1091" t="inlineStr">
@@ -71747,6 +72012,11 @@
           <t>00:00:35.962</t>
         </is>
       </c>
+      <c r="R1106" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
     </row>
     <row r="1107">
       <c r="A1107" t="inlineStr">
@@ -73955,6 +74225,11 @@
           <t>00:00:33.298</t>
         </is>
       </c>
+      <c r="R1140" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
       <c r="S1140" t="inlineStr">
         <is>
           <t>45844</t>
@@ -78001,6 +78276,11 @@
           <t>84718</t>
         </is>
       </c>
+      <c r="S1201" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="1202">
       <c r="A1202" t="inlineStr">
@@ -80026,6 +80306,11 @@
           <t>00:01:46.562</t>
         </is>
       </c>
+      <c r="S1231" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="1232">
       <c r="A1232" t="inlineStr">
@@ -83061,6 +83346,11 @@
           <t>00:01:37.276</t>
         </is>
       </c>
+      <c r="S1277" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
     </row>
     <row r="1278">
       <c r="A1278" t="inlineStr">
@@ -83381,6 +83671,11 @@
           <t>00:01:51.870</t>
         </is>
       </c>
+      <c r="R1282" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
     </row>
     <row r="1283">
       <c r="A1283" t="inlineStr">
@@ -84366,6 +84661,11 @@
           <t>52286</t>
         </is>
       </c>
+      <c r="S1297" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
     </row>
     <row r="1298">
       <c r="A1298" t="inlineStr">
@@ -85545,6 +85845,11 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="T1314" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="1315">
       <c r="A1315" t="inlineStr">
@@ -85890,6 +86195,11 @@
           <t>00:02:58.264</t>
         </is>
       </c>
+      <c r="R1319" t="inlineStr">
+        <is>
+          <t>36598</t>
+        </is>
+      </c>
     </row>
     <row r="1320">
       <c r="A1320" t="inlineStr">
@@ -87992,6 +88302,11 @@
           <t>42059</t>
         </is>
       </c>
+      <c r="T1347" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
     </row>
     <row r="1348">
       <c r="A1348" t="inlineStr">
@@ -88133,6 +88448,11 @@
       <c r="P1349" t="inlineStr">
         <is>
           <t>00:03:00.333</t>
+        </is>
+      </c>
+      <c r="R1349" t="inlineStr">
+        <is>
+          <t>36598</t>
         </is>
       </c>
     </row>
@@ -89191,7 +89511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D262"/>
+  <dimension ref="A1:D274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -94958,6 +95278,270 @@
         </is>
       </c>
     </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>36175</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Viktor</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>MELANTEV</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>36596</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Miika</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>NYKAENEN</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>36598</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Pauliina</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>POLET</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>42045</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Aleh</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>YURENIA</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>42058</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Volha</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>KHUDZENKA</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>42063</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Aliksandr</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>LIAPIOSHKA</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>42161</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Kenny</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>WALLACE</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>42358</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Timothy</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>HORNSBY</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>42463</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Chris</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>MEHAK</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>42735</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Nelson Roberto</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>GERINGER SALLETE</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>53064</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Benjamin</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>HEFNER</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>68923</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Tohir</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>NURMUHAMMADI</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Duisburg_2012_WC/Duisburg_2012_WC_Results.xlsx
+++ b/events/Duisburg_2012_WC/Duisburg_2012_WC_Results.xlsx
@@ -2513,11 +2513,6 @@
           <t>00:02:04.102</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
-        <is>
-          <t>47779</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -8722,11 +8717,6 @@
           <t>00:04:13.008</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr">
-        <is>
-          <t>47779</t>
-        </is>
-      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -14322,11 +14312,6 @@
           <t>00:02:01.631</t>
         </is>
       </c>
-      <c r="R217" t="inlineStr">
-        <is>
-          <t>47779</t>
-        </is>
-      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -24498,11 +24483,6 @@
           <t>00:01:58.177</t>
         </is>
       </c>
-      <c r="R376" t="inlineStr">
-        <is>
-          <t>84718</t>
-        </is>
-      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -31940,11 +31920,6 @@
           <t>00:02:22.039</t>
         </is>
       </c>
-      <c r="R490" t="inlineStr">
-        <is>
-          <t>84718</t>
-        </is>
-      </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -34866,11 +34841,6 @@
           <t>00:01:56.916</t>
         </is>
       </c>
-      <c r="R535" t="inlineStr">
-        <is>
-          <t>47779</t>
-        </is>
-      </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -38975,11 +38945,6 @@
           <t>00:04:06.162</t>
         </is>
       </c>
-      <c r="R597" t="inlineStr">
-        <is>
-          <t>47779</t>
-        </is>
-      </c>
     </row>
     <row r="598">
       <c r="A598" t="inlineStr">
@@ -57289,11 +57254,6 @@
           <t>00:00:37.287</t>
         </is>
       </c>
-      <c r="R878" t="inlineStr">
-        <is>
-          <t>84718</t>
-        </is>
-      </c>
       <c r="S878" t="inlineStr">
         <is>
           <t>36175</t>
@@ -78271,11 +78231,6 @@
           <t>00:00:37.596</t>
         </is>
       </c>
-      <c r="R1201" t="inlineStr">
-        <is>
-          <t>84718</t>
-        </is>
-      </c>
       <c r="S1201" t="inlineStr">
         <is>
           <t>36175</t>
@@ -82562,11 +82517,6 @@
           <t>00:01:57.736</t>
         </is>
       </c>
-      <c r="R1265" t="inlineStr">
-        <is>
-          <t>84718</t>
-        </is>
-      </c>
     </row>
     <row r="1266">
       <c r="A1266" t="inlineStr">
@@ -87619,11 +87569,6 @@
       <c r="P1338" t="inlineStr">
         <is>
           <t>00:02:51.568</t>
-        </is>
-      </c>
-      <c r="S1338" t="inlineStr">
-        <is>
-          <t>84718</t>
         </is>
       </c>
     </row>
@@ -89511,7 +89456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D274"/>
+  <dimension ref="A1:D272"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95237,39 +95182,39 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>36175</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Krisztina</t>
+          <t>Viktor</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>BEDOCS</t>
+          <t>MELANTEV</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>84718</t>
+          <t>36596</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Nikolay</t>
+          <t>Miika</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>LIPKIN</t>
+          <t>NYKAENEN</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -95281,39 +95226,39 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>36175</t>
+          <t>36598</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Viktor</t>
+          <t>Pauliina</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>MELANTEV</t>
+          <t>POLET</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>F</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>36596</t>
+          <t>42045</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Miika</t>
+          <t>Aleh</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>NYKAENEN</t>
+          <t>YURENIA</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -95325,17 +95270,17 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>36598</t>
+          <t>42058</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Pauliina</t>
+          <t>Volha</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>POLET</t>
+          <t>KHUDZENKA</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -95347,17 +95292,17 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>42045</t>
+          <t>42063</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>Aleh</t>
+          <t>Aliksandr</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>YURENIA</t>
+          <t>LIAPIOSHKA</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -95369,39 +95314,39 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>42058</t>
+          <t>42161</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Volha</t>
+          <t>Kenny</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>KHUDZENKA</t>
+          <t>WALLACE</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>M</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>42063</t>
+          <t>42358</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Aliksandr</t>
+          <t>Timothy</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>LIAPIOSHKA</t>
+          <t>HORNSBY</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -95413,17 +95358,17 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>42161</t>
+          <t>42463</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Kenny</t>
+          <t>Chris</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>WALLACE</t>
+          <t>MEHAK</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -95435,17 +95380,17 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>42358</t>
+          <t>42735</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Timothy</t>
+          <t>Nelson Roberto</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>HORNSBY</t>
+          <t>GERINGER SALLETE</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -95457,17 +95402,17 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>42463</t>
+          <t>53064</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Chris</t>
+          <t>Benjamin</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>MEHAK</t>
+          <t>HEFNER</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -95479,64 +95424,20 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>42735</t>
+          <t>68923</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Nelson Roberto</t>
+          <t>Tohir</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>GERINGER SALLETE</t>
+          <t>NURMUHAMMADI</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="273">
-      <c r="A273" t="inlineStr">
-        <is>
-          <t>53064</t>
-        </is>
-      </c>
-      <c r="B273" t="inlineStr">
-        <is>
-          <t>Benjamin</t>
-        </is>
-      </c>
-      <c r="C273" t="inlineStr">
-        <is>
-          <t>HEFNER</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr">
-        <is>
-          <t>M</t>
-        </is>
-      </c>
-    </row>
-    <row r="274">
-      <c r="A274" t="inlineStr">
-        <is>
-          <t>68923</t>
-        </is>
-      </c>
-      <c r="B274" t="inlineStr">
-        <is>
-          <t>Tohir</t>
-        </is>
-      </c>
-      <c r="C274" t="inlineStr">
-        <is>
-          <t>NURMUHAMMADI</t>
-        </is>
-      </c>
-      <c r="D274" t="inlineStr">
         <is>
           <t>M</t>
         </is>

--- a/events/Duisburg_2012_WC/Duisburg_2012_WC_Results.xlsx
+++ b/events/Duisburg_2012_WC/Duisburg_2012_WC_Results.xlsx
@@ -7522,6 +7522,11 @@
           <t>00:04:49.661</t>
         </is>
       </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -25548,6 +25553,11 @@
           <t>00:02:09.882</t>
         </is>
       </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -32480,6 +32490,11 @@
           <t>00:02:14.763</t>
         </is>
       </c>
+      <c r="R499" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
@@ -50291,6 +50306,11 @@
           <t>00:00:46.235</t>
         </is>
       </c>
+      <c r="R769" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
     </row>
     <row r="770">
       <c r="A770" t="inlineStr">
@@ -63914,6 +63934,11 @@
           <t>00:00:46.028</t>
         </is>
       </c>
+      <c r="R981" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
     </row>
     <row r="982">
       <c r="A982" t="inlineStr">
@@ -82835,6 +82860,11 @@
       <c r="P1270" t="inlineStr">
         <is>
           <t>00:02:07.331</t>
+        </is>
+      </c>
+      <c r="R1270" t="inlineStr">
+        <is>
+          <t>51939</t>
         </is>
       </c>
     </row>
@@ -89456,7 +89486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D272"/>
+  <dimension ref="A1:D273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95443,6 +95473,28 @@
         </is>
       </c>
     </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>51939</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Vicente</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Gonzales</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/events/Duisburg_2012_WC/Duisburg_2012_WC_Results.xlsx
+++ b/events/Duisburg_2012_WC/Duisburg_2012_WC_Results.xlsx
@@ -25238,6 +25238,11 @@
           <t>00:01:52.227</t>
         </is>
       </c>
+      <c r="R388" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -32050,6 +32055,11 @@
           <t>00:02:02.107</t>
         </is>
       </c>
+      <c r="R492" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -49496,6 +49506,11 @@
           <t>00:00:40.787</t>
         </is>
       </c>
+      <c r="R756" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="757">
       <c r="A757" t="inlineStr">
@@ -63494,6 +63509,11 @@
           <t>00:00:42.042</t>
         </is>
       </c>
+      <c r="R974" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="975">
       <c r="A975" t="inlineStr">
@@ -76591,6 +76611,11 @@
           <t>00:00:41.203</t>
         </is>
       </c>
+      <c r="R1176" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
     </row>
     <row r="1177">
       <c r="A1177" t="inlineStr">
@@ -83912,6 +83937,11 @@
       <c r="P1286" t="inlineStr">
         <is>
           <t>00:01:54.017</t>
+        </is>
+      </c>
+      <c r="R1286" t="inlineStr">
+        <is>
+          <t>36633</t>
         </is>
       </c>
     </row>
@@ -89486,7 +89516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D273"/>
+  <dimension ref="A1:D274"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -95495,6 +95525,28 @@
         </is>
       </c>
     </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>36633</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Nivalter</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Santos</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
